--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.184853553771973</v>
+        <v>3.168201208114624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9778329373515132</v>
+        <v>0.9937950196146749</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9920505871725384</v>
+        <v>0.9917649260714955</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999016135379771</v>
+        <v>0.999929723955698</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 0.01, 'class_weight': None, 'max_iter': 2000, 'penalty': None, 'solver': 'lbfgs'}</t>
+          <t>{'C': 0.01, 'class_weight': 'balanced', 'max_iter': 1000, 'penalty': None, 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -526,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.41702342033386</v>
+        <v>5.827354907989502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9860832868623287</v>
+        <v>0.9936940240824083</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -538,11 +538,11 @@
         <v>0.9917649260714955</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999578343734189</v>
+        <v>0.999929723955698</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 10, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.184853553771973</v>
+        <v>3.168201208114624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9778329373515132</v>
+        <v>0.9937950196146749</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9920505871725384</v>
+        <v>0.9917649260714955</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999016135379771</v>
+        <v>0.999929723955698</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 0.01, 'class_weight': None, 'max_iter': 2000, 'penalty': None, 'solver': 'lbfgs'}</t>
+          <t>{'C': 0.01, 'class_weight': 'balanced', 'max_iter': 1000, 'penalty': None, 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.41702342033386</v>
+        <v>5.827354907989502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9860832868623287</v>
+        <v>0.9936940240824083</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -669,11 +669,11 @@
         <v>0.9917649260714955</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999578343734189</v>
+        <v>0.999929723955698</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 10, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.168201208114624</v>
+        <v>0.8491902351379395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9937950196146749</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999929723955698</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 0.01, 'class_weight': 'balanced', 'max_iter': 1000, 'penalty': None, 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.827354907989502</v>
+        <v>1.251380681991577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9936940240824083</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.999929723955698</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 10, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.168201208114624</v>
+        <v>0.8491902351379395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9937950196146749</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999929723955698</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 0.01, 'class_weight': 'balanced', 'max_iter': 1000, 'penalty': None, 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.827354907989502</v>
+        <v>1.251380681991577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9936940240824083</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.999929723955698</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 10, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8491902351379395</v>
+        <v>5.685605764389038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8088321925942394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8503401360544217</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7670055721647685</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9662871951501688</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.3, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.251380681991577</v>
+        <v>8.213213682174683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8038242609318094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8503401360544217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7670055721647685</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9661136563468925</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.5, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19.34123420715332</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.801080840267115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8639455782312925</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7875531593106022</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9662293488824101</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'C': 10, 'class_weight': None, 'l1_ratio': 0.7, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8491902351379395</v>
+        <v>5.685605764389038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8088321925942394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8503401360544217</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7670055721647685</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9662871951501688</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.3, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.251380681991577</v>
+        <v>8.213213682174683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8038242609318094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8503401360544217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7670055721647685</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9661136563468925</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.5, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19.34123420715332</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.801080840267115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8639455782312925</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7875531593106022</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9662293488824101</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'C': 10, 'class_weight': None, 'l1_ratio': 0.7, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.685605764389038</v>
+        <v>84.12868881225586</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8088321925942394</v>
+        <v>0.7319187167195951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8503401360544217</v>
+        <v>0.8299769850402762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7670055721647685</v>
+        <v>0.7391667698284974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9662871951501688</v>
+        <v>0.8593011597658791</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.3, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.213213682174683</v>
+        <v>220.4796578884125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8038242609318094</v>
+        <v>0.7328853331272454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8503401360544217</v>
+        <v>0.8288262370540852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7670055721647685</v>
+        <v>0.7371274467075601</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9661136563468925</v>
+        <v>0.8584015282896162</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.5, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>19.34123420715332</v>
+        <v>361.8796882629395</v>
       </c>
       <c r="E4" t="n">
-        <v>0.801080840267115</v>
+        <v>0.7330116584649267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8639455782312925</v>
+        <v>0.830264672036824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7875531593106022</v>
+        <v>0.739472389794956</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9662293488824101</v>
+        <v>0.8594352915673099</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'C': 10, 'class_weight': None, 'l1_ratio': 0.7, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.685605764389038</v>
+        <v>84.12868881225586</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8088321925942394</v>
+        <v>0.7319187167195951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8503401360544217</v>
+        <v>0.8299769850402762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7670055721647685</v>
+        <v>0.7391667698284974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9662871951501688</v>
+        <v>0.8593011597658791</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.3, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.213213682174683</v>
+        <v>220.4796578884125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8038242609318094</v>
+        <v>0.7328853331272454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8503401360544217</v>
+        <v>0.8288262370540852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7670055721647685</v>
+        <v>0.7371274467075601</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9661136563468925</v>
+        <v>0.8584015282896162</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'l1_ratio': 0.5, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>19.34123420715332</v>
+        <v>361.8796882629395</v>
       </c>
       <c r="E4" t="n">
-        <v>0.801080840267115</v>
+        <v>0.7330116584649267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8639455782312925</v>
+        <v>0.830264672036824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7875531593106022</v>
+        <v>0.739472389794956</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9662293488824101</v>
+        <v>0.8594352915673099</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'C': 10, 'class_weight': None, 'l1_ratio': 0.7, 'max_iter': 2000, 'penalty': 'elasticnet', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>84.12868881225586</v>
+        <v>1.091411828994751</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7319187167195951</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8299769850402762</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7391667698284974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8593011597658791</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>220.4796578884125</v>
+        <v>1.596763134002686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328853331272454</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8288262370540852</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7371274467075601</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8584015282896162</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>361.8796882629395</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7330116584649267</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.830264672036824</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.739472389794956</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8594352915673099</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>84.12868881225586</v>
+        <v>1.091411828994751</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7319187167195951</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8299769850402762</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7391667698284974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8593011597658791</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>220.4796578884125</v>
+        <v>1.596763134002686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328853331272454</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8288262370540852</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7371274467075601</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8584015282896162</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>361.8796882629395</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7330116584649267</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.830264672036824</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.739472389794956</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8594352915673099</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.091411828994751</v>
+        <v>0.8362832069396973</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.596763134002686</v>
+        <v>1.175803661346436</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.091411828994751</v>
+        <v>0.8362832069396973</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.596763134002686</v>
+        <v>1.175803661346436</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8362832069396973</v>
+        <v>0.8281044960021973</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.175803661346436</v>
+        <v>1.20138955116272</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8362832069396973</v>
+        <v>0.8281044960021973</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.175803661346436</v>
+        <v>1.20138955116272</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,10 +491,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8281044960021973</v>
+        <v>0.211564302444458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.20138955116272</v>
+        <v>0.4227964878082275</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8281044960021973</v>
+        <v>0.211564302444458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.20138955116272</v>
+        <v>0.4227964878082275</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.211564302444458</v>
+        <v>26.82263731956482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4227964878082275</v>
+        <v>89.91980266571045</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.211564302444458</v>
+        <v>26.82263731956482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4227964878082275</v>
+        <v>89.91980266571045</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>26.82263731956482</v>
+        <v>30.93723678588867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.33279315941173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.571875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.2822276124859151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9054765625000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>89.91980266571045</v>
+        <v>47.34295010566711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.340650031081789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.571875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.2822276124859151</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9054765625000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>26.82263731956482</v>
+        <v>30.93723678588867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.33279315941173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.571875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.2822276124859151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9054765625000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>89.91980266571045</v>
+        <v>47.34295010566711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.340650031081789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.571875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.2822276124859151</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9054765625000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.93723678588867</v>
+        <v>1.760576009750366</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33279315941173</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.571875</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2822276124859151</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9054765625000001</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.34295010566711</v>
+        <v>3.360211372375488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.340650031081789</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.571875</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2822276124859151</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9054765625000001</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.93723678588867</v>
+        <v>1.760576009750366</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33279315941173</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.571875</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2822276124859151</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9054765625000001</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>47.34295010566711</v>
+        <v>3.360211372375488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.340650031081789</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.571875</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2822276124859151</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9054765625000001</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.760576009750366</v>
+        <v>0.1705286502838135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.360211372375488</v>
+        <v>0.3486030101776123</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7939449541284403</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.760576009750366</v>
+        <v>0.1705286502838135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.360211372375488</v>
+        <v>0.3486030101776123</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7939449541284403</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1705286502838135</v>
+        <v>0.1674644947052002</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3486030101776123</v>
+        <v>0.3419375419616699</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1705286502838135</v>
+        <v>0.1674644947052002</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3486030101776123</v>
+        <v>0.3419375419616699</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1674644947052002</v>
+        <v>0.168318510055542</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3419375419616699</v>
+        <v>0.3358554840087891</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1674644947052002</v>
+        <v>0.168318510055542</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3419375419616699</v>
+        <v>0.3358554840087891</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.168318510055542</v>
+        <v>0.316514253616333</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3358554840087891</v>
+        <v>0.4219343662261963</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -543,6 +543,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.122652053833008</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.168318510055542</v>
+        <v>0.316514253616333</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3358554840087891</v>
+        <v>0.4219343662261963</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -674,6 +709,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.122652053833008</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.316514253616333</v>
+        <v>0.2196180820465088</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4219343662261963</v>
+        <v>0.4867086410522461</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.122652053833008</v>
+        <v>1.127304553985596</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967124678275436</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.316514253616333</v>
+        <v>0.2196180820465088</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4219343662261963</v>
+        <v>0.4867086410522461</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.122652053833008</v>
+        <v>1.127304553985596</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967124678275436</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2196180820465088</v>
+        <v>14.07042956352234</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4867086410522461</v>
+        <v>29.15627408027649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.127304553985596</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967124678275436</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2196180820465088</v>
+        <v>14.07042956352234</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4867086410522461</v>
+        <v>29.15627408027649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.127304553985596</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967124678275436</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.07042956352234</v>
+        <v>50.32587075233459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.9998055964130637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.15627408027649</v>
+        <v>118.0428924560547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.9997407969867332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.07042956352234</v>
+        <v>50.32587075233459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.9998055964130637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.15627408027649</v>
+        <v>118.0428924560547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.9997407969867332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>50.32587075233459</v>
+        <v>44.24955129623413</v>
       </c>
       <c r="E2" t="n">
         <v>0.9998055964130637</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>118.0428924560547</v>
+        <v>103.1700747013092</v>
       </c>
       <c r="E3" t="n">
         <v>0.9997407969867332</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>50.32587075233459</v>
+        <v>44.24955129623413</v>
       </c>
       <c r="E2" t="n">
         <v>0.9998055964130637</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>118.0428924560547</v>
+        <v>103.1700747013092</v>
       </c>
       <c r="E3" t="n">
         <v>0.9997407969867332</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>44.24955129623413</v>
+        <v>1.879142999649048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998055964130637</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1700747013092</v>
+        <v>3.306220293045044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997407969867332</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>44.24955129623413</v>
+        <v>1.879142999649048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998055964130637</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1700747013092</v>
+        <v>3.306220293045044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997407969867332</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.879142999649048</v>
+        <v>129.834644317627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9053356399652978</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.306220293045044</v>
+        <v>222.530154466629</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9051087342385802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7939449541284403</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.879142999649048</v>
+        <v>129.834644317627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9053356399652978</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.306220293045044</v>
+        <v>222.530154466629</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9051087342385802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7939449541284403</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>129.834644317627</v>
+        <v>70.75936245918274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9053356399652978</v>
+        <v>0.2961390255365762</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2721936515775019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8458810565042343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>222.530154466629</v>
+        <v>139.754597902298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9051087342385802</v>
+        <v>0.2921261617486491</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4581632653061224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2728290119081531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8460117312231015</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>129.834644317627</v>
+        <v>70.75936245918274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9053356399652978</v>
+        <v>0.2961390255365762</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2721936515775019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8458810565042343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>222.530154466629</v>
+        <v>139.754597902298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9051087342385802</v>
+        <v>0.2921261617486491</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4581632653061224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2728290119081531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8460117312231015</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>70.75936245918274</v>
+        <v>0.2339539527893066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2961390255365762</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2721936515775019</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8458810565042343</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>139.754597902298</v>
+        <v>0.4850766658782959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2921261617486491</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4581632653061224</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2728290119081531</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8460117312231015</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.103629589080811</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>70.75936245918274</v>
+        <v>0.2339539527893066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2961390255365762</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2721936515775019</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8458810565042343</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>139.754597902298</v>
+        <v>0.4850766658782959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2921261617486491</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4581632653061224</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2728290119081531</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8460117312231015</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.103629589080811</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2339539527893066</v>
+        <v>0.3077001571655273</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4850766658782959</v>
+        <v>0.5751190185546875</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.103629589080811</v>
+        <v>1.336190223693848</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967124678275436</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2339539527893066</v>
+        <v>0.3077001571655273</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4850766658782959</v>
+        <v>0.5751190185546875</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.103629589080811</v>
+        <v>1.336190223693848</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967124678275436</v>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3077001571655273</v>
+        <v>1.472885608673096</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7659440168113942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7800675675675676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7661955415100101</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8462693670562074</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5751190185546875</v>
+        <v>2.926017999649048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7666973234670946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7800675675675676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7661955415100101</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8462693670562074</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.336190223693848</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967124678275436</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3077001571655273</v>
+        <v>1.472885608673096</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7659440168113942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7800675675675676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7661955415100101</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8462693670562074</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5751190185546875</v>
+        <v>2.926017999649048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7666973234670946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.7800675675675676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7661955415100101</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8462693670562074</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.336190223693848</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967124678275436</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472885608673096</v>
+        <v>61.29657006263733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7659440168113942</v>
+        <v>0.9999436686941007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.9998873493297286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7661955415100101</v>
+        <v>0.9998873490080773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8462693670562074</v>
+        <v>0.9999999619293707</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.926017999649048</v>
+        <v>128.7283976078033</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7666973234670946</v>
+        <v>0.9999155034749145</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.9998873493297286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7661955415100101</v>
+        <v>0.9998873490080773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8462693670562074</v>
+        <v>0.9999999619293707</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472885608673096</v>
+        <v>61.29657006263733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7659440168113942</v>
+        <v>0.9999436686941007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.9998873493297286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7661955415100101</v>
+        <v>0.9998873490080773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8462693670562074</v>
+        <v>0.9999999619293707</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.926017999649048</v>
+        <v>128.7283976078033</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7666973234670946</v>
+        <v>0.9999155034749145</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.9998873493297286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7661955415100101</v>
+        <v>0.9998873490080773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8462693670562074</v>
+        <v>0.9999999619293707</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.29657006263733</v>
+        <v>40.58893442153931</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999436686941007</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>128.7283976078033</v>
+        <v>88.34208679199219</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999155034749145</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.29657006263733</v>
+        <v>40.58893442153931</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999436686941007</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>128.7283976078033</v>
+        <v>88.34208679199219</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999155034749145</v>
